--- a/data_extactor/batch_10_fa/trimmed/batch_0084_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0084_fa_trim.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار نمایش نقشه‌های فنی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار ثبت ساعت کار و حضور و غیاب</t>
+          <t>Autodesk AutoCAD | Blueprint display software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | چابکی انگشتان | چابکی دستی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دقت کنترل</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های رباتیک | مونتاژکاران گروهی</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های رباتیک | مونتاژکاران گروهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و نقشه‌کشی رایانه‌ای CADD | Dassault Systemes SolidWorks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP</t>
+          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes SolidWorks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | تجسم فضایی | هماهنگی چند عضو بدن | دقت کنترل</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | تجسم | هماهنگی چند عضو | دقت کنترل</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دیگ‌سازان (بویلرسازان) | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | متخصصان نصب و راه‌اندازی ماشین‌آلات صنعتی (Millwrights) | سازندگان و مونتاژکاران سازه‌های فلزی</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و نقشه‌کشی رایانه‌ای CADD | Dassault Systemes CATIA | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی</t>
+          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes CATIA | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | دید نزدیک | قدرت ایستا | هماهنگی چند عضو بدن | دقت کنترل | چابکی دستی | تجسم فضایی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دیگ‌سازان (بویلرسازان) | ماشین‌کاران | آرماتوربندان | کارگران ورق‌کاری | اسکلت‌سازان سازه‌های فلزی و فولادی | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | آرماتوربندان و نصابان میلگرد | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | آموزش و پرورش | شیمی | زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | آموزش و پرورش | شیمی | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | پایداری دست و بازو | هماهنگی چند عضو بدن | قدرت بالاتنه | دید نزدیک | دقت کنترل | چابکی دستی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | دقت کنترل | مهارت دستی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه‌ای | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و صیقل‌کاران دستی | قالب‌ریزان و شکل‌دهندگان، به‌جز فلز و پلاستیک | کارگران رنگ‌آمیزی صنعتی، پوشش‌دهی و تزیین | سازندگان و مونتاژکاران سازه‌های فلزی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | پایداری دست و بازو | دید نزدیک | چابکی دستی | حساسیت به مسئله | دقت کنترل | تجسم فضایی</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | دقت کنترل | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | پرداخت‌کاران و صیقل‌کاران دستی | ماشین‌کاران | قالب‌سازان و ابزارسازان صنعتی | تعمیرکاران ساعت دیواری و مچی</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | قالب‌سازان و ابزارسازان صنعتی | تعمیرکاران ساعت‌های مچی و دیواری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | دید نزدیک | مرتب‌سازی اطلاعات | پایداری دست و بازو | حساسیت به مسئله | دقت کنترل</t>
+          <t>مهارت دستی | مهارت انگشتان | بینایی نزدیک | ترتیب‌دهی اطلاعات | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سرپرستان رده اول کارگران تولید و عملیات | مکانیک‌های ماشین‌آلات صنعتی | بازرسان، آزمایش‌گران، تفکیک‌کنندگان، نمونه‌برداران و وزن‌کنندگان در خط تولید | تکنسین‌های رباتیک</t>
+          <t>مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سرپرستان رده اول کارگران تولید و عملیات | مکانیک‌های ماشین‌آلات صنعتی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چند عضو بدن | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران گروهی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران | کارگران ساده تولید</t>
+          <t>مونتاژکاران گروهی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | کمک‌کارگران خطوط تولید</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | یادگیری فعال | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و خدمات فردی | تولید مواد غذایی | زبان انگلیسی | ریاضیات</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | تشخیص رنگ‌ها | حساسیت به مسئله | دقت کنترل | چابکی انگشتان | چابکی دستی</t>
+          <t>بینایی نزدیک | درک شفاهی | تشخیص رنگ بصری | حساسیت به مسئله | دقت کنترل | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرآشپزان و سرآشپزان ارشد | آشپزان رستوران | مسئولان آماده‌سازی و ترکیب فرمولاسیون مواد غذایی (Food Batchmakers) | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی غذا | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن صنعتی | بسته‌بندهای دستی</t>
+          <t>سرآشپزان و آشپزان ارشد | آشپزان رستوران | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران بسته‌بندی دستی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | تولید و فرآوری | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | پایداری دست و بازو | دقت کنترل | حساسیت به مسئله | قدرت بالاتنه | چابکی انگشتان</t>
+          <t>بینایی نزدیک | مهارت دستی | ثبات دست و بازو | دقت کنترل | حساسیت به مسئله | قدرت تنه | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | آشپزان رستوران | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | سلاخان و کارگران کشتارگاه و بسته‌بندی گوشت</t>
+          <t>نانوایان و شیرینی‌پزان | آشپزان رستوران | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | قصابان و بسته‌بندی‌کنندگان گوشت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | تولید مواد غذایی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و امور اداری | مکانیک</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | دقت کنترل | دید نزدیک | قدرت بالاتنه | چابکی دستی | توجه انتخابی | چابکی انگشتان</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | قدرت تنه | مهارت دستی | توجه انتخابی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>قصابان و برش‌کاران گوشت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردایش و آسیاب مواد غذایی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس مواد غذایی | کارگران مزارع پرورش دام، طیور و آبزی‌پروری | کارگران آماده‌سازی غذا | بسته‌بندهای دستی | سلاخان و کارگران کشتارگاه و بسته‌بندی گوشت</t>
+          <t>قصابان و برش‌کاران گوشت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | کارگران پرورش دام، طیور و آبزیان | کارگران آماده‌سازی غذا | کارگران بسته‌بندی دستی | قصابان و بسته‌بندی‌کنندگان گوشت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
